--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -371,7 +371,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,12 +382,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -419,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -449,9 +443,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1091,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="11">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1513,7 +1504,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>

--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="113">
   <si>
     <t>time_step_number</t>
   </si>
@@ -413,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -443,6 +443,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -836,7 +839,7 @@
         <v>112</v>
       </c>
       <c r="C4" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -1075,7 +1078,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -1099,10 +1102,18 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>104</v>
       </c>
     </row>

--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -258,7 +258,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,12 +269,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -306,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -326,14 +320,8 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,7 +629,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="14.862142857142858" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -653,7 +641,7 @@
       <c r="A1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -676,7 +664,7 @@
       <c r="A2" s="3">
         <v>21</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3">
@@ -692,18 +680,18 @@
         <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>23</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -715,14 +703,14 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>24</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
@@ -738,12 +726,12 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3"/>
-      <c r="B5" s="8"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -784,7 +772,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">

--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -677,10 +677,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -723,10 +723,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">

--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -731,22 +731,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -772,13 +772,13 @@
         <v>1e-07</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
@@ -804,13 +804,13 @@
         <v>1e-08</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,22 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,14 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,34 +48,13 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -168,34 +133,34 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -209,71 +174,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -297,53 +260,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -353,7 +317,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -362,7 +326,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -371,7 +335,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -379,10 +343,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -411,7 +375,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -424,12 +388,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -449,682 +414,595 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.29071428571429" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
-    <col width="14.86214285714286" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TYPE_ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ELEMENT_TYPE</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>OPTION1</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OPTION2</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>OPTION3</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>OPTION4</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OPTION5</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CP_ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>EMF</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>VOLT</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="3" t="n">
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>VOLT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.14785714285714" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MATERIAL_ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MUR_X</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MUR_Y</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MUR_Z</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>RHO_X</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RHO_Y</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RHO_Z</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>M_X</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>M_Y</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>M_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>1e-07</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
         <v>1e-07</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" t="n">
         <v>1e-07</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>1e-08</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" t="n">
         <v>1e-08</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" t="n">
         <v>1e-08</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21.14785714285714" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="7" max="7"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="8" max="8"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="11" max="11"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="12" max="12"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="6" min="13" max="13"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="14" max="14"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="15" max="15"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="16" max="16"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="17" max="17"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="18" max="18"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="19" max="19"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="20" max="20"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CONSTANTS_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>THK</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TURNS</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>VOL</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>T_X</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>T_Y</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>T_Z</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>V_X</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>V_Y</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>V_Z</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>OMEGA_X</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>OMEGA_Y</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>OMEGA_Z</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>LOC_X</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LOC_Y</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LOC_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.04</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
         <v>50</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3" t="n">
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="12.14785714285714" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SETTING</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ksp_type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>preonly</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>pc_type</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>lu</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>initial_linear_tolerance</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>1e-06</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>max_linear_iterations</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>minimum_linear_tolerance</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>1e-10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1"/>
-    <row r="8" ht="18.75" customHeight="1"/>
-    <row r="9" ht="18.75" customHeight="1"/>
-    <row r="10" ht="18.75" customHeight="1"/>
-    <row r="11" ht="18.75" customHeight="1"/>
-    <row r="12" ht="18.75" customHeight="1"/>
-    <row r="13" ht="18.75" customHeight="1"/>
-    <row r="14" ht="18.75" customHeight="1"/>
-    <row r="15" ht="18.75" customHeight="1"/>
-    <row r="16" ht="18.75" customHeight="1"/>
-    <row r="17" ht="18.75" customHeight="1"/>
-    <row r="18" ht="18.75" customHeight="1"/>
-    <row r="19" ht="18.75" customHeight="1"/>
-    <row r="20" ht="18.75" customHeight="1"/>
-    <row r="21" ht="18.75" customHeight="1"/>
-    <row r="22" ht="18.75" customHeight="1"/>
-    <row r="23" ht="18.75" customHeight="1"/>
-    <row r="24" ht="18.75" customHeight="1"/>
-    <row r="25" ht="18.75" customHeight="1"/>
-    <row r="26" ht="18.75" customHeight="1"/>
-    <row r="27" ht="18.75" customHeight="1"/>
-    <row r="28" ht="18.75" customHeight="1"/>
-    <row r="29" ht="18.75" customHeight="1"/>
-    <row r="30" ht="18.75" customHeight="1"/>
-    <row r="31" ht="18.75" customHeight="1"/>
-    <row r="32" ht="18.75" customHeight="1"/>
-    <row r="33" ht="18.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tests/coil_2D_avoltemf/input_template.xlsx
+++ b/tests/coil_2D_avoltemf/input_template.xlsx
@@ -474,7 +474,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
